--- a/Input/Noor_Takaful/benefits.xlsx
+++ b/Input/Noor_Takaful/benefits.xlsx
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
   <si>
     <t xml:space="preserve">PlanName</t>
   </si>
   <si>
-    <t xml:space="preserve">Network Provider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Name</t>
+    <t xml:space="preserve">Network Details</t>
   </si>
   <si>
     <t xml:space="preserve">Annual Limit</t>
@@ -37,10 +34,10 @@
     <t xml:space="preserve">Geographical Coverage</t>
   </si>
   <si>
-    <t xml:space="preserve">Inpatient (Hospitalisation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accomodation</t>
+    <t xml:space="preserve">In-patient (Hospitalization &amp; Surgery)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accommodation Type</t>
   </si>
   <si>
     <t xml:space="preserve">Out-patient benefits</t>
@@ -52,10 +49,10 @@
     <t xml:space="preserve">Emergency Evacuation</t>
   </si>
   <si>
-    <t xml:space="preserve">Chronic Conditions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-existing Cover</t>
+    <t xml:space="preserve">Chronic Condition Cover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-existing Condition Cover</t>
   </si>
   <si>
     <t xml:space="preserve">Routine Maternity</t>
@@ -127,10 +124,7 @@
     <t xml:space="preserve">Plan 1</t>
   </si>
   <si>
-    <t xml:space="preserve">NAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VN (OP restricted to clinics)</t>
+    <t xml:space="preserve">NAS VN (OP restricted to clinics)</t>
   </si>
   <si>
     <t xml:space="preserve">AED 75,000</t>
@@ -187,7 +181,7 @@
     <t xml:space="preserve">Noor Takaful - Northern Emirates</t>
   </si>
   <si>
-    <t xml:space="preserve">Northern emirates</t>
+    <t xml:space="preserve">NE</t>
   </si>
   <si>
     <t xml:space="preserve">Plan 2</t>
@@ -222,7 +216,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -249,6 +243,11 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -293,12 +292,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -331,16 +334,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AI3"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="33" min="1" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="22.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="15.14"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="36" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="32" min="1" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="22.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="15.14"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="35" style="0" width="11.52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="46.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -353,10 +356,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -368,10 +371,10 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -420,18 +423,18 @@
         <v>25</v>
       </c>
       <c r="AA1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="AC1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="0" t="s">
         <v>28</v>
       </c>
       <c r="AF1" s="0" t="s">
@@ -446,202 +449,193 @@
       <c r="AI1" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="AJ1" s="0" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="72.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" s="4"/>
+      <c r="S2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="V2" s="4"/>
+      <c r="W2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI2" s="5" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="2" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N2" s="1" t="s">
+      <c r="N3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R3" s="4"/>
+      <c r="S3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="V3" s="4"/>
+      <c r="W3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="P2" s="1" t="s">
+      <c r="X3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="S2" s="3"/>
-      <c r="T2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="W2" s="3"/>
-      <c r="X2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Z2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF2" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ2" s="4" t="s">
+      <c r="AA3" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="S3" s="3"/>
-      <c r="T3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="W3" s="3"/>
-      <c r="X3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="AB3" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
